--- a/data/customers.xlsx
+++ b/data/customers.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고객DB" sheetId="1" r:id="R7387a626b7814c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고객DB" sheetId="1" r:id="R7d2b6021a5e4452e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -41,42 +41,14 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="2">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -104,36 +76,6 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -142,7 +84,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CustomersTable" displayName="CustomersTable" ref="A1:J73" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CustomersTable" displayName="CustomersTable" ref="A1:J134" headerRowCount="1">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="등록일시"/>
     <x:tableColumn id="2" name="등록경로"/>
@@ -321,39 +263,39 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>등록일시</x:v>
       </x:c>
-      <x:c r="B1" s="15" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>등록경로</x:v>
       </x:c>
-      <x:c r="C1" s="15" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>성명</x:v>
       </x:c>
-      <x:c r="D1" s="15" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>닉네임</x:v>
       </x:c>
-      <x:c r="E1" s="15" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>전화번호</x:v>
       </x:c>
-      <x:c r="F1" s="15" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>우편번호</x:v>
       </x:c>
-      <x:c r="G1" s="15" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>기본주소</x:v>
       </x:c>
-      <x:c r="H1" s="15" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>상세주소</x:v>
       </x:c>
-      <x:c r="I1" s="15" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>배송요청사항</x:v>
       </x:c>
-      <x:c r="J1" s="16" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>고객ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="17" t="str">
+      <x:c r="A2" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:29:55</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
@@ -380,12 +322,12 @@
       <x:c r="I2" s="10" t="str">
         <x:v>현관문앞에두세요</x:v>
       </x:c>
-      <x:c r="J2" s="18" t="str">
+      <x:c r="J2" s="10" t="str">
         <x:v>mryuyt13</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="17" t="str">
+      <x:c r="A3" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:36:28</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
@@ -412,12 +354,12 @@
       <x:c r="I3" s="10" t="str">
         <x:v>문앞</x:v>
       </x:c>
-      <x:c r="J3" s="18" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>mryv788e</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="17" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:27:44</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
@@ -442,12 +384,12 @@
         <x:v>402호</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str"/>
-      <x:c r="J4" s="18" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>mryuw03v</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="17" t="str">
+      <x:c r="A5" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:27:49</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
@@ -472,12 +414,12 @@
       <x:c r="I5" s="10" t="str">
         <x:v>문 앞</x:v>
       </x:c>
-      <x:c r="J5" s="18" t="str">
+      <x:c r="J5" s="10" t="str">
         <x:v>mryuw40b</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="17" t="str">
+      <x:c r="A6" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:32:37</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
@@ -500,12 +442,12 @@
       </x:c>
       <x:c r="H6" s="10" t="str"/>
       <x:c r="I6" s="10" t="str"/>
-      <x:c r="J6" s="18" t="str">
+      <x:c r="J6" s="10" t="str">
         <x:v>mryv29w2</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="17" t="str">
+      <x:c r="A7" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:36:00</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
@@ -530,12 +472,12 @@
         <x:v>성욱철강</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str"/>
-      <x:c r="J7" s="18" t="str">
+      <x:c r="J7" s="10" t="str">
         <x:v>8c0751ca-2a52-441c-8045-dd01b7ad2641</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="17" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:38:54</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
@@ -560,12 +502,12 @@
         <x:v>천연염색</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str"/>
-      <x:c r="J8" s="18" t="str">
+      <x:c r="J8" s="10" t="str">
         <x:v>dd5575cf-4f68-4f78-b40d-b30802e7d83b</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="17" t="str">
+      <x:c r="A9" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:40:17</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
@@ -590,12 +532,12 @@
         <x:v>1층</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str"/>
-      <x:c r="J9" s="18" t="str">
+      <x:c r="J9" s="10" t="str">
         <x:v>mryvc55a</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="17" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:40:53</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
@@ -620,12 +562,12 @@
         <x:v>202호</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str"/>
-      <x:c r="J10" s="18" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>f2377938-88f5-4278-8b40-e5d88f0928b9</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="17" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:41:22</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
@@ -652,12 +594,12 @@
       <x:c r="I11" s="10" t="str">
         <x:v>대문앞</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="str">
+      <x:c r="J11" s="10" t="str">
         <x:v>mryvdjd6</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="17" t="str">
+      <x:c r="A12" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:41:25</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
@@ -682,12 +624,12 @@
         <x:v>영호길 42-37</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str"/>
-      <x:c r="J12" s="18" t="str">
+      <x:c r="J12" s="10" t="str">
         <x:v>mryvdkyu</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="17" t="str">
+      <x:c r="A13" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:42:09</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
@@ -710,12 +652,12 @@
       </x:c>
       <x:c r="H13" s="10" t="str"/>
       <x:c r="I13" s="10" t="str"/>
-      <x:c r="J13" s="18" t="str">
+      <x:c r="J13" s="10" t="str">
         <x:v>3a657929-f979-4eeb-b949-cb8eee6b620e</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="17" t="str">
+      <x:c r="A14" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:43:30</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
@@ -738,12 +680,12 @@
       </x:c>
       <x:c r="H14" s="10" t="str"/>
       <x:c r="I14" s="10" t="str"/>
-      <x:c r="J14" s="18" t="str">
+      <x:c r="J14" s="10" t="str">
         <x:v>2ba0a8d1-9f15-43cd-9ab1-9d5e6d3d7bc3</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="17" t="str">
+      <x:c r="A15" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:47:40</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
@@ -768,12 +710,12 @@
         <x:v>104-2501호</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str"/>
-      <x:c r="J15" s="18" t="str">
+      <x:c r="J15" s="10" t="str">
         <x:v>84c375d8-39a6-4dee-a20b-d8a9b936b8f7</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="17" t="str">
+      <x:c r="A16" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:51:27</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
@@ -796,12 +738,12 @@
       </x:c>
       <x:c r="H16" s="10" t="str"/>
       <x:c r="I16" s="10" t="str"/>
-      <x:c r="J16" s="18" t="str">
+      <x:c r="J16" s="10" t="str">
         <x:v>ff724bae-2a67-49b6-aa01-c76a84ced175</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="17" t="str">
+      <x:c r="A17" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:53:14</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
@@ -828,12 +770,12 @@
       <x:c r="I17" s="10" t="str">
         <x:v>출입비번 종 8136</x:v>
       </x:c>
-      <x:c r="J17" s="18" t="str">
+      <x:c r="J17" s="10" t="str">
         <x:v>325a303b-569c-4ceb-8dc0-eb5f5e5a95c9</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="17" t="str">
+      <x:c r="A18" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:53:57</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
@@ -860,12 +802,12 @@
       <x:c r="I18" s="10" t="str">
         <x:v>문앞</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="str">
+      <x:c r="J18" s="10" t="str">
         <x:v>mryvtq6a</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="17" t="str">
+      <x:c r="A19" s="10" t="str">
         <x:v>2026. 7. 24. 오후 8:54:59</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
@@ -890,12 +832,12 @@
         <x:v>롯데마트입구 콩마켓앞</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str"/>
-      <x:c r="J19" s="18" t="str">
+      <x:c r="J19" s="10" t="str">
         <x:v>2dafe8d2-dd95-4ed3-ad3e-20ded03712d7</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="17" t="str">
+      <x:c r="A20" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:32:45</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
@@ -920,13 +862,13 @@
         <x:v>예미지아파트 414동407호</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str"/>
-      <x:c r="J20" s="18" t="str">
+      <x:c r="J20" s="10" t="str">
         <x:v>mryx7m5k</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="17" t="str">
-        <x:v>2026. 7. 24. 오후 8:57:23</x:v>
+      <x:c r="A21" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:03:05</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
         <x:v>관리자폼</x:v>
@@ -935,7 +877,7 @@
         <x:v>심규찬</x:v>
       </x:c>
       <x:c r="D21" s="10" t="str">
-        <x:v>심규찬</x:v>
+        <x:v>규찬심</x:v>
       </x:c>
       <x:c r="E21" s="12" t="str">
         <x:v>010 3525 0313</x:v>
@@ -950,22 +892,22 @@
         <x:v>602동702호</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str"/>
-      <x:c r="J21" s="18" t="str">
-        <x:v>56c3b879-22a4-4e31-a553-c13fdafdd8cf</x:v>
+      <x:c r="J21" s="10" t="str">
+        <x:v>3eba0791-4084-4064-9edd-f5d513f8f584</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="17" t="str">
-        <x:v>2026. 7. 24. 오후 8:59:19</x:v>
+      <x:c r="A22" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:08:36</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
         <x:v>관리자폼</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>김프로</x:v>
+        <x:v>김민수</x:v>
       </x:c>
       <x:c r="D22" s="10" t="str">
-        <x:v>김프로</x:v>
+        <x:v>김프로님</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
         <x:v>010-3555-2979</x:v>
@@ -980,12 +922,12 @@
         <x:v>105동601호</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str"/>
-      <x:c r="J22" s="18" t="str">
-        <x:v>07f42bba-1628-4b61-9dab-2f0e9fe6085a</x:v>
+      <x:c r="J22" s="10" t="str">
+        <x:v>d3f382f5-f480-41bc-a027-7965ce22780a</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="17" t="str">
+      <x:c r="A23" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:00:14</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
@@ -1010,12 +952,12 @@
         <x:v>3동1406호</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str"/>
-      <x:c r="J23" s="18" t="str">
+      <x:c r="J23" s="10" t="str">
         <x:v>38acc59b-cead-4b57-8c31-56d400cf646b</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="17" t="str">
+      <x:c r="A24" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:00:53</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
@@ -1040,12 +982,12 @@
         <x:v>104동1104호</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str"/>
-      <x:c r="J24" s="18" t="str">
+      <x:c r="J24" s="10" t="str">
         <x:v>fcff74f0-d29d-4273-9de2-4b57b86d7c4d</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="17" t="str">
+      <x:c r="A25" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:01:34</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
@@ -1070,12 +1012,12 @@
         <x:v>202호</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str"/>
-      <x:c r="J25" s="18" t="str">
+      <x:c r="J25" s="10" t="str">
         <x:v>365b43c7-657a-47f6-b2a8-fd714d9272bc</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="17" t="str">
+      <x:c r="A26" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:02:21</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
@@ -1100,12 +1042,12 @@
         <x:v>102동1204호</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str"/>
-      <x:c r="J26" s="18" t="str">
+      <x:c r="J26" s="10" t="str">
         <x:v>5be314f3-58f1-4edd-9147-eb07ab027e4b</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="17" t="str">
+      <x:c r="A27" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:03:21</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
@@ -1130,12 +1072,12 @@
         <x:v>302호</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str"/>
-      <x:c r="J27" s="18" t="str">
+      <x:c r="J27" s="10" t="str">
         <x:v>d94e9a81-c253-4187-8d48-b16e547951cc</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="17" t="str">
+      <x:c r="A28" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:04:36</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
@@ -1160,12 +1102,12 @@
         <x:v>107동306호</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str"/>
-      <x:c r="J28" s="18" t="str">
+      <x:c r="J28" s="10" t="str">
         <x:v>344bd698-d6fe-472d-91ba-ec7ed2f483b3</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="17" t="str">
+      <x:c r="A29" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:05:39</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
@@ -1190,12 +1132,12 @@
         <x:v>101동510호</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str"/>
-      <x:c r="J29" s="18" t="str">
+      <x:c r="J29" s="10" t="str">
         <x:v>354deb46-f742-416f-9642-ef69bce9bc2c</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="17" t="str">
+      <x:c r="A30" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:06:34</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
@@ -1220,12 +1162,12 @@
         <x:v>305호</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str"/>
-      <x:c r="J30" s="18" t="str">
+      <x:c r="J30" s="10" t="str">
         <x:v>d1ff7312-aae9-41cd-9bfe-6feeab7b4315</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="17" t="str">
+      <x:c r="A31" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:07:36</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
@@ -1250,12 +1192,12 @@
         <x:v>103동302호</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str"/>
-      <x:c r="J31" s="18" t="str">
+      <x:c r="J31" s="10" t="str">
         <x:v>24dfe437-2db3-4a0b-a76b-1a10a3809f2e</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="17" t="str">
+      <x:c r="A32" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:08:57</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
@@ -1280,12 +1222,12 @@
         <x:v>203동1902호</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str"/>
-      <x:c r="J32" s="18" t="str">
+      <x:c r="J32" s="10" t="str">
         <x:v>f7264668-2ee3-4667-9cba-7ac853204f55</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="17" t="str">
+      <x:c r="A33" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:11:44</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
@@ -1312,12 +1254,12 @@
       <x:c r="I33" s="10" t="str">
         <x:v>수고많으십니다 배송 후 문자 부탁드립니다</x:v>
       </x:c>
-      <x:c r="J33" s="18" t="str">
+      <x:c r="J33" s="10" t="str">
         <x:v>mrywgmus</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="17" t="str">
+      <x:c r="A34" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:23:31</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
@@ -1342,12 +1284,12 @@
         <x:v>LH아파트 308동911호</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str"/>
-      <x:c r="J34" s="18" t="str">
+      <x:c r="J34" s="10" t="str">
         <x:v>mrywvq13</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="17" t="str">
+      <x:c r="A35" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:24:53</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
@@ -1372,12 +1314,12 @@
         <x:v>106동306호</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str"/>
-      <x:c r="J35" s="18" t="str">
+      <x:c r="J35" s="10" t="str">
         <x:v>mrywxhpf</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="17" t="str">
+      <x:c r="A36" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:26:10</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
@@ -1402,12 +1344,12 @@
         <x:v>102동709호</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str"/>
-      <x:c r="J36" s="18" t="str">
+      <x:c r="J36" s="10" t="str">
         <x:v>1cb457fd-68eb-41b9-934b-1396599be24d</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="17" t="str">
+      <x:c r="A37" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:26:27</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
@@ -1434,12 +1376,12 @@
       <x:c r="I37" s="10" t="str">
         <x:v>문안쪽</x:v>
       </x:c>
-      <x:c r="J37" s="18" t="str">
+      <x:c r="J37" s="10" t="str">
         <x:v>mrywzirf</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="17" t="str">
+      <x:c r="A38" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:28:53</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
@@ -1464,12 +1406,12 @@
       <x:c r="I38" s="10" t="str">
         <x:v>문앞</x:v>
       </x:c>
-      <x:c r="J38" s="18" t="str">
+      <x:c r="J38" s="10" t="str">
         <x:v>mryx2nlb</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="17" t="str">
+      <x:c r="A39" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:29:20</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
@@ -1492,12 +1434,12 @@
       </x:c>
       <x:c r="H39" s="10" t="str"/>
       <x:c r="I39" s="10" t="str"/>
-      <x:c r="J39" s="18" t="str">
+      <x:c r="J39" s="10" t="str">
         <x:v>1e87600d-514d-45fd-82b2-075624491ea7</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="17" t="str">
+      <x:c r="A40" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:29:30</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
@@ -1524,12 +1466,12 @@
       <x:c r="I40" s="10" t="str">
         <x:v>문앞</x:v>
       </x:c>
-      <x:c r="J40" s="18" t="str">
+      <x:c r="J40" s="10" t="str">
         <x:v>mryx3f90</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="17" t="str">
+      <x:c r="A41" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:29:39</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
@@ -1554,12 +1496,12 @@
         <x:v>가동 102호</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str"/>
-      <x:c r="J41" s="18" t="str">
+      <x:c r="J41" s="10" t="str">
         <x:v>mryx3m03</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="17" t="str">
+      <x:c r="A42" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:30:00</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
@@ -1584,12 +1526,12 @@
         <x:v>101동203호</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str"/>
-      <x:c r="J42" s="18" t="str">
+      <x:c r="J42" s="10" t="str">
         <x:v>4343a37b-67d5-476d-8546-bf82f6745bff</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="17" t="str">
+      <x:c r="A43" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:30:05</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
@@ -1614,12 +1556,12 @@
         <x:v>상동</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str"/>
-      <x:c r="J43" s="18" t="str">
+      <x:c r="J43" s="10" t="str">
         <x:v>mryx4675</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="17" t="str">
+      <x:c r="A44" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:30:15</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
@@ -1646,12 +1588,12 @@
       <x:c r="I44" s="10" t="str">
         <x:v>문앞</x:v>
       </x:c>
-      <x:c r="J44" s="18" t="str">
+      <x:c r="J44" s="10" t="str">
         <x:v>mryx4e83</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="17" t="str">
+      <x:c r="A45" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:31:16</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
@@ -1676,12 +1618,12 @@
         <x:v>206동1203호</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str"/>
-      <x:c r="J45" s="18" t="str">
+      <x:c r="J45" s="10" t="str">
         <x:v>0037e522-cbac-4af3-a948-42d2ba7245be</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="17" t="str">
+      <x:c r="A46" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:32:03</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
@@ -1708,12 +1650,12 @@
       <x:c r="I46" s="10" t="str">
         <x:v>문앞</x:v>
       </x:c>
-      <x:c r="J46" s="18" t="str">
+      <x:c r="J46" s="10" t="str">
         <x:v>mryx6phd</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="17" t="str">
+      <x:c r="A47" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:32:42</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
@@ -1738,12 +1680,12 @@
         <x:v>103동401호</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str"/>
-      <x:c r="J47" s="18" t="str">
+      <x:c r="J47" s="10" t="str">
         <x:v>b7ba0bd4-dc75-4420-b3c5-2c92177be8ad</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="17" t="str">
+      <x:c r="A48" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:33:50</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
@@ -1768,12 +1710,12 @@
         <x:v>214동1705호</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str"/>
-      <x:c r="J48" s="18" t="str">
+      <x:c r="J48" s="10" t="str">
         <x:v>94d78e6e-3646-49ed-8e40-8b673eaa0102</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="17" t="str">
+      <x:c r="A49" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:34:58</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
@@ -1798,12 +1740,12 @@
         <x:v>206동1302호</x:v>
       </x:c>
       <x:c r="I49" s="10" t="str"/>
-      <x:c r="J49" s="18" t="str">
+      <x:c r="J49" s="10" t="str">
         <x:v>e49ff79b-5c9f-4fee-848f-51622efd95f5</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="17" t="str">
+      <x:c r="A50" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:36:02</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
@@ -1828,12 +1770,12 @@
         <x:v>명품하이츠405호</x:v>
       </x:c>
       <x:c r="I50" s="10" t="str"/>
-      <x:c r="J50" s="18" t="str">
+      <x:c r="J50" s="10" t="str">
         <x:v>bdb976ce-d7dc-4b62-8626-78bf43e71f75</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="17" t="str">
+      <x:c r="A51" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:36:34</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
@@ -1856,12 +1798,12 @@
       </x:c>
       <x:c r="H51" s="10" t="str"/>
       <x:c r="I51" s="10" t="str"/>
-      <x:c r="J51" s="18" t="str">
+      <x:c r="J51" s="10" t="str">
         <x:v>bdba8cb4-1dac-4eb3-a278-ba70effd8024</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="17" t="str">
+      <x:c r="A52" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:37:47</x:v>
       </x:c>
       <x:c r="B52" s="10" t="str">
@@ -1886,12 +1828,12 @@
         <x:v>105동401호</x:v>
       </x:c>
       <x:c r="I52" s="10" t="str"/>
-      <x:c r="J52" s="18" t="str">
+      <x:c r="J52" s="10" t="str">
         <x:v>c98fab08-cfac-4558-ac9b-313693ee56f7</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="17" t="str">
+      <x:c r="A53" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:38:47</x:v>
       </x:c>
       <x:c r="B53" s="10" t="str">
@@ -1916,12 +1858,12 @@
         <x:v>비플러스마켓</x:v>
       </x:c>
       <x:c r="I53" s="10" t="str"/>
-      <x:c r="J53" s="18" t="str">
+      <x:c r="J53" s="10" t="str">
         <x:v>4b79c143-32d3-4279-99e5-25801f7805e4</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="17" t="str">
+      <x:c r="A54" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:39:53</x:v>
       </x:c>
       <x:c r="B54" s="10" t="str">
@@ -1946,12 +1888,12 @@
         <x:v>101동1306호</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str"/>
-      <x:c r="J54" s="18" t="str">
+      <x:c r="J54" s="10" t="str">
         <x:v>071c6dc6-829e-4e83-a286-af5df59b591f</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="17" t="str">
+      <x:c r="A55" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:40:37</x:v>
       </x:c>
       <x:c r="B55" s="10" t="str">
@@ -1976,12 +1918,12 @@
         <x:v>102동 601호 (송림동, 진로아파트).</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str"/>
-      <x:c r="J55" s="18" t="str">
+      <x:c r="J55" s="10" t="str">
         <x:v>mryxhpys</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="17" t="str">
+      <x:c r="A56" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:41:06</x:v>
       </x:c>
       <x:c r="B56" s="10" t="str">
@@ -2006,13 +1948,13 @@
         <x:v>101동1001호</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str"/>
-      <x:c r="J56" s="18" t="str">
+      <x:c r="J56" s="10" t="str">
         <x:v>0b7e937e-1d0b-413b-a55d-be7fab1bbca4</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="17" t="str">
-        <x:v>2026. 7. 24. 오후 9:41:49</x:v>
+      <x:c r="A57" s="10" t="str">
+        <x:v>2026. 7. 25. 오전 12:03:38</x:v>
       </x:c>
       <x:c r="B57" s="10" t="str">
         <x:v>관리자폼</x:v>
@@ -2021,7 +1963,7 @@
         <x:v>김혜숙</x:v>
       </x:c>
       <x:c r="D57" s="10" t="str">
-        <x:v>이쁜혜숙</x:v>
+        <x:v>혜숙김</x:v>
       </x:c>
       <x:c r="E57" s="12" t="str">
         <x:v>01094014570</x:v>
@@ -2033,15 +1975,15 @@
         <x:v>대전 동구 흥룡로71번길 7</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>목련빌304호</x:v>
+        <x:v>304호</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str"/>
-      <x:c r="J57" s="18" t="str">
-        <x:v>0e9ead92-6c67-4b45-b4b2-5184031a621c</x:v>
+      <x:c r="J57" s="10" t="str">
+        <x:v>f39e6d57-fc99-4380-b469-eb5cf7a14871</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="17" t="str">
+      <x:c r="A58" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:42:35</x:v>
       </x:c>
       <x:c r="B58" s="10" t="str">
@@ -2066,12 +2008,12 @@
         <x:v>115동707호</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str"/>
-      <x:c r="J58" s="18" t="str">
+      <x:c r="J58" s="10" t="str">
         <x:v>6eb36fbb-5337-4d68-8e43-6e992378094c</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="17" t="str">
+      <x:c r="A59" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:43:32</x:v>
       </x:c>
       <x:c r="B59" s="10" t="str">
@@ -2096,12 +2038,12 @@
         <x:v>116동503호</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str"/>
-      <x:c r="J59" s="18" t="str">
+      <x:c r="J59" s="10" t="str">
         <x:v>b19f308e-815b-413b-aa10-3735638b2ffe</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="17" t="str">
+      <x:c r="A60" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:44:31</x:v>
       </x:c>
       <x:c r="B60" s="10" t="str">
@@ -2126,12 +2068,12 @@
         <x:v>205호</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str"/>
-      <x:c r="J60" s="18" t="str">
+      <x:c r="J60" s="10" t="str">
         <x:v>639f8597-1c3a-4627-bd97-8bdc0670d9db</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="17" t="str">
+      <x:c r="A61" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:45:13</x:v>
       </x:c>
       <x:c r="B61" s="10" t="str">
@@ -2156,12 +2098,12 @@
         <x:v>104동604호</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str"/>
-      <x:c r="J61" s="18" t="str">
+      <x:c r="J61" s="10" t="str">
         <x:v>9ea8cc62-f951-4faa-9c01-ce34e1c1764d</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="17" t="str">
+      <x:c r="A62" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:45:46</x:v>
       </x:c>
       <x:c r="B62" s="10" t="str">
@@ -2184,12 +2126,12 @@
       </x:c>
       <x:c r="H62" s="10" t="str"/>
       <x:c r="I62" s="10" t="str"/>
-      <x:c r="J62" s="18" t="str">
+      <x:c r="J62" s="10" t="str">
         <x:v>7bc52078-dd5c-421c-a61e-21201772df9e</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="17" t="str">
+      <x:c r="A63" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:46:23</x:v>
       </x:c>
       <x:c r="B63" s="10" t="str">
@@ -2212,12 +2154,12 @@
       </x:c>
       <x:c r="H63" s="10" t="str"/>
       <x:c r="I63" s="10" t="str"/>
-      <x:c r="J63" s="18" t="str">
+      <x:c r="J63" s="10" t="str">
         <x:v>9cc1f088-1289-4a6b-a0ce-c67e262e8e0e</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="17" t="str">
+      <x:c r="A64" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:47:04</x:v>
       </x:c>
       <x:c r="B64" s="10" t="str">
@@ -2242,12 +2184,12 @@
         <x:v>D동 302호</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str"/>
-      <x:c r="J64" s="18" t="str">
+      <x:c r="J64" s="10" t="str">
         <x:v>04fbbd07-f6f0-4bc1-bb1b-d3d362d30c97</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="17" t="str">
+      <x:c r="A65" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:47:37</x:v>
       </x:c>
       <x:c r="B65" s="10" t="str">
@@ -2272,12 +2214,12 @@
         <x:v>102동1404호</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str"/>
-      <x:c r="J65" s="18" t="str">
+      <x:c r="J65" s="10" t="str">
         <x:v>510405e3-111b-42e6-ad8f-f45adc73be89</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="17" t="str">
+      <x:c r="A66" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:52:07</x:v>
       </x:c>
       <x:c r="B66" s="10" t="str">
@@ -2304,12 +2246,12 @@
       <x:c r="I66" s="10" t="str">
         <x:v>배송 전 문자 / 현관 비번:5995*</x:v>
       </x:c>
-      <x:c r="J66" s="18" t="str">
+      <x:c r="J66" s="10" t="str">
         <x:v>mryxwio2</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="17" t="str">
+      <x:c r="A67" s="10" t="str">
         <x:v>2026. 7. 24. 오후 9:59:50</x:v>
       </x:c>
       <x:c r="B67" s="10" t="str">
@@ -2334,12 +2276,12 @@
         <x:v>1층</x:v>
       </x:c>
       <x:c r="I67" s="10" t="str"/>
-      <x:c r="J67" s="18" t="str">
+      <x:c r="J67" s="10" t="str">
         <x:v>mryy6fmn</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="17" t="str">
+      <x:c r="A68" s="10" t="str">
         <x:v>2026. 7. 24. 오후 10:10:19</x:v>
       </x:c>
       <x:c r="B68" s="10" t="str">
@@ -2364,12 +2306,12 @@
         <x:v>102동801호</x:v>
       </x:c>
       <x:c r="I68" s="10" t="str"/>
-      <x:c r="J68" s="18" t="str">
+      <x:c r="J68" s="10" t="str">
         <x:v>cec10344-5c33-45a2-9217-662e71e28c81</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="17" t="str">
+      <x:c r="A69" s="10" t="str">
         <x:v>2026. 7. 24. 오후 10:11:15</x:v>
       </x:c>
       <x:c r="B69" s="10" t="str">
@@ -2394,12 +2336,12 @@
         <x:v>102호 더라이트티비</x:v>
       </x:c>
       <x:c r="I69" s="10" t="str"/>
-      <x:c r="J69" s="18" t="str">
+      <x:c r="J69" s="10" t="str">
         <x:v>3bfa4795-af6b-4557-a110-09be3b6618b3</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="17" t="str">
+      <x:c r="A70" s="10" t="str">
         <x:v>2026. 7. 24. 오후 10:12:18</x:v>
       </x:c>
       <x:c r="B70" s="10" t="str">
@@ -2424,12 +2366,12 @@
         <x:v>105동904호</x:v>
       </x:c>
       <x:c r="I70" s="10" t="str"/>
-      <x:c r="J70" s="18" t="str">
+      <x:c r="J70" s="10" t="str">
         <x:v>39598f48-c96d-4d70-9250-f4ade2d39600</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="17" t="str">
+      <x:c r="A71" s="10" t="str">
         <x:v>2026. 7. 24. 오후 10:13:10</x:v>
       </x:c>
       <x:c r="B71" s="10" t="str">
@@ -2454,12 +2396,12 @@
         <x:v>한빛그린아파트 901호</x:v>
       </x:c>
       <x:c r="I71" s="10" t="str"/>
-      <x:c r="J71" s="18" t="str">
+      <x:c r="J71" s="10" t="str">
         <x:v>6115c4b3-b0c9-4442-af91-d49376407c7f</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="17" t="str">
+      <x:c r="A72" s="10" t="str">
         <x:v>2026. 7. 24. 오후 10:14:28</x:v>
       </x:c>
       <x:c r="B72" s="10" t="str">
@@ -2484,44 +2426,1838 @@
         <x:v>동일빌라 b동401호</x:v>
       </x:c>
       <x:c r="I72" s="10" t="str"/>
-      <x:c r="J72" s="18" t="str">
+      <x:c r="J72" s="10" t="str">
         <x:v>ce7a2157-5044-423e-82bd-3623f1eccc44</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="19" t="str">
+      <x:c r="A73" s="10" t="str">
         <x:v>2026. 7. 24. 오후 10:15:32</x:v>
       </x:c>
-      <x:c r="B73" s="20" t="str">
-        <x:v>관리자폼</x:v>
-      </x:c>
-      <x:c r="C73" s="20" t="str">
+      <x:c r="B73" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C73" s="10" t="str">
         <x:v>박영숙</x:v>
       </x:c>
-      <x:c r="D73" s="20" t="str">
+      <x:c r="D73" s="10" t="str">
         <x:v>폴리박</x:v>
       </x:c>
-      <x:c r="E73" s="21" t="str">
+      <x:c r="E73" s="12" t="str">
         <x:v>010 4878 1433</x:v>
       </x:c>
-      <x:c r="F73" s="21" t="str">
+      <x:c r="F73" s="12" t="str">
         <x:v>31104</x:v>
       </x:c>
-      <x:c r="G73" s="20" t="str">
+      <x:c r="G73" s="10" t="str">
         <x:v>충남 천안시 서북구 봉정로 324</x:v>
       </x:c>
-      <x:c r="H73" s="20" t="str">
+      <x:c r="H73" s="10" t="str">
         <x:v>106동3202호</x:v>
       </x:c>
-      <x:c r="I73" s="20" t="str"/>
-      <x:c r="J73" s="22" t="str">
+      <x:c r="I73" s="10" t="str"/>
+      <x:c r="J73" s="10" t="str">
         <x:v>2d4cf6ef-290d-444f-a458-f2d282bbb82a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 10:46:57</x:v>
+      </x:c>
+      <x:c r="B74" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="str">
+        <x:v>심혜련</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="str">
+        <x:v>하흠</x:v>
+      </x:c>
+      <x:c r="E74" s="12" t="str">
+        <x:v>010-8392-4504</x:v>
+      </x:c>
+      <x:c r="F74" s="12" t="str">
+        <x:v>31217</x:v>
+      </x:c>
+      <x:c r="G74" s="10" t="str">
+        <x:v>충남 천안시 동남구 풍세면 풍세산단로 290</x:v>
+      </x:c>
+      <x:c r="H74" s="10" t="str">
+        <x:v>112동1805호</x:v>
+      </x:c>
+      <x:c r="I74" s="10" t="str">
+        <x:v>공동현관비번 #1805#0305</x:v>
+      </x:c>
+      <x:c r="J74" s="10" t="str">
+        <x:v>fc70da66-e9ae-4667-97f1-262095667df0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:16:47</x:v>
+      </x:c>
+      <x:c r="B75" s="10" t="str">
+        <x:v>가입폼</x:v>
+      </x:c>
+      <x:c r="C75" s="10" t="str">
+        <x:v>박경단</x:v>
+      </x:c>
+      <x:c r="D75" s="10" t="str">
+        <x:v>마이쥬</x:v>
+      </x:c>
+      <x:c r="E75" s="12" t="str">
+        <x:v>01077584345</x:v>
+      </x:c>
+      <x:c r="F75" s="12" t="str">
+        <x:v>52788</x:v>
+      </x:c>
+      <x:c r="G75" s="10" t="str">
+        <x:v>경남 진주시 동진로131번길 9-11</x:v>
+      </x:c>
+      <x:c r="H75" s="10" t="str">
+        <x:v>202호</x:v>
+      </x:c>
+      <x:c r="I75" s="10" t="str"/>
+      <x:c r="J75" s="10" t="str">
+        <x:v>mrz0xe6a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 10:58:20</x:v>
+      </x:c>
+      <x:c r="B76" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C76" s="10" t="str">
+        <x:v>김미라</x:v>
+      </x:c>
+      <x:c r="D76" s="10" t="str">
+        <x:v>44녀</x:v>
+      </x:c>
+      <x:c r="E76" s="12" t="str">
+        <x:v>010-5295-3442</x:v>
+      </x:c>
+      <x:c r="F76" s="12" t="str">
+        <x:v>61417</x:v>
+      </x:c>
+      <x:c r="G76" s="10" t="str">
+        <x:v>전남광주통합특별시 동구 산수길35번길 13</x:v>
+      </x:c>
+      <x:c r="H76" s="10" t="str">
+        <x:v>2층</x:v>
+      </x:c>
+      <x:c r="I76" s="10" t="str"/>
+      <x:c r="J76" s="10" t="str">
+        <x:v>ae5f9cc9-32f0-4af9-ab9a-8e9213ab4587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 10:59:15</x:v>
+      </x:c>
+      <x:c r="B77" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C77" s="10" t="str">
+        <x:v>은봉기</x:v>
+      </x:c>
+      <x:c r="D77" s="10" t="str">
+        <x:v>가시고기</x:v>
+      </x:c>
+      <x:c r="E77" s="12" t="str">
+        <x:v>010-3652-3333</x:v>
+      </x:c>
+      <x:c r="F77" s="12" t="str">
+        <x:v>55096</x:v>
+      </x:c>
+      <x:c r="G77" s="10" t="str">
+        <x:v>전북특별자치도 전주시 완산구 유기전1길 6-11</x:v>
+      </x:c>
+      <x:c r="H77" s="10" t="str">
+        <x:v>3층</x:v>
+      </x:c>
+      <x:c r="I77" s="10" t="str"/>
+      <x:c r="J77" s="10" t="str">
+        <x:v>8cc7a0bc-0f03-4282-ae9e-7356ba0d9ff8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:00:27</x:v>
+      </x:c>
+      <x:c r="B78" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C78" s="10" t="str">
+        <x:v>김대욱</x:v>
+      </x:c>
+      <x:c r="D78" s="10" t="str">
+        <x:v>곰두리82</x:v>
+      </x:c>
+      <x:c r="E78" s="12" t="str">
+        <x:v>010-3137-5508</x:v>
+      </x:c>
+      <x:c r="F78" s="12" t="str">
+        <x:v>12713</x:v>
+      </x:c>
+      <x:c r="G78" s="10" t="str">
+        <x:v>경기 광주시 퇴촌면 천진암로 613</x:v>
+      </x:c>
+      <x:c r="H78" s="10" t="str">
+        <x:v>이마트24 광주퇴촌점</x:v>
+      </x:c>
+      <x:c r="I78" s="10" t="str"/>
+      <x:c r="J78" s="10" t="str">
+        <x:v>735e827b-ba81-4291-8778-ce1b7c025761</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:01:36</x:v>
+      </x:c>
+      <x:c r="B79" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C79" s="10" t="str">
+        <x:v>김혁순</x:v>
+      </x:c>
+      <x:c r="D79" s="10" t="str">
+        <x:v>구룡포1</x:v>
+      </x:c>
+      <x:c r="E79" s="12" t="str">
+        <x:v>010-6205-7797</x:v>
+      </x:c>
+      <x:c r="F79" s="12" t="str">
+        <x:v>12036</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str">
+        <x:v>경기 남양주시 오남읍 진건오남로 806-34</x:v>
+      </x:c>
+      <x:c r="H79" s="10" t="str">
+        <x:v>3층 미화원실앞</x:v>
+      </x:c>
+      <x:c r="I79" s="10" t="str"/>
+      <x:c r="J79" s="10" t="str">
+        <x:v>01846953-430f-4a2a-b509-747575fbcac0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:04:54</x:v>
+      </x:c>
+      <x:c r="B80" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C80" s="10" t="str">
+        <x:v>김운영</x:v>
+      </x:c>
+      <x:c r="D80" s="10" t="str">
+        <x:v>김나비a</x:v>
+      </x:c>
+      <x:c r="E80" s="12" t="str">
+        <x:v>010-8401-4135</x:v>
+      </x:c>
+      <x:c r="F80" s="12" t="str">
+        <x:v>17029</x:v>
+      </x:c>
+      <x:c r="G80" s="10" t="str">
+        <x:v>경기 용인시 처인구 포곡읍 백옥대로1910번길 20-1</x:v>
+      </x:c>
+      <x:c r="H80" s="10" t="str">
+        <x:v>도사빌라 비동 301호</x:v>
+      </x:c>
+      <x:c r="I80" s="10" t="str"/>
+      <x:c r="J80" s="10" t="str">
+        <x:v>61f2a7a2-c7c2-4b41-8ac9-031595dc1007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:05:37</x:v>
+      </x:c>
+      <x:c r="B81" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C81" s="10" t="str">
+        <x:v>김대</x:v>
+      </x:c>
+      <x:c r="D81" s="10" t="str">
+        <x:v>김대</x:v>
+      </x:c>
+      <x:c r="E81" s="12" t="str">
+        <x:v>010-8531-5970</x:v>
+      </x:c>
+      <x:c r="F81" s="12" t="str">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="G81" s="10" t="str">
+        <x:v>부산 금정구 중앙대로 2128-25</x:v>
+      </x:c>
+      <x:c r="H81" s="10" t="str">
+        <x:v>401호</x:v>
+      </x:c>
+      <x:c r="I81" s="10" t="str"/>
+      <x:c r="J81" s="10" t="str">
+        <x:v>63513ce7-5296-4011-97ec-3836500a97eb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:06:48</x:v>
+      </x:c>
+      <x:c r="B82" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C82" s="10" t="str">
+        <x:v>김사라</x:v>
+      </x:c>
+      <x:c r="D82" s="10" t="str">
+        <x:v>김욱</x:v>
+      </x:c>
+      <x:c r="E82" s="12" t="str">
+        <x:v>010-4503-8464</x:v>
+      </x:c>
+      <x:c r="F82" s="12" t="str">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="G82" s="10" t="str">
+        <x:v>부산 금정구 중앙대로1841번안길 21-2</x:v>
+      </x:c>
+      <x:c r="H82" s="10" t="str"/>
+      <x:c r="I82" s="10" t="str"/>
+      <x:c r="J82" s="10" t="str">
+        <x:v>aaed8add-462a-450e-99b0-8affa86d2def</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:07:49</x:v>
+      </x:c>
+      <x:c r="B83" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C83" s="10" t="str">
+        <x:v>김종훈</x:v>
+      </x:c>
+      <x:c r="D83" s="10" t="str">
+        <x:v>김종훈</x:v>
+      </x:c>
+      <x:c r="E83" s="12" t="str">
+        <x:v>010-5059-5281</x:v>
+      </x:c>
+      <x:c r="F83" s="12" t="str">
+        <x:v>25818</x:v>
+      </x:c>
+      <x:c r="G83" s="10" t="str">
+        <x:v>강원특별자치도 동해시 배골길 32-4</x:v>
+      </x:c>
+      <x:c r="H83" s="10" t="str">
+        <x:v>104동1103호</x:v>
+      </x:c>
+      <x:c r="I83" s="10" t="str"/>
+      <x:c r="J83" s="10" t="str">
+        <x:v>7530c60b-1409-40f9-9533-6f9efc47a142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:09:23</x:v>
+      </x:c>
+      <x:c r="B84" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C84" s="10" t="str">
+        <x:v>정성남</x:v>
+      </x:c>
+      <x:c r="D84" s="10" t="str">
+        <x:v>남이youtube</x:v>
+      </x:c>
+      <x:c r="E84" s="12" t="str">
+        <x:v>010-5673-9929</x:v>
+      </x:c>
+      <x:c r="F84" s="12" t="str">
+        <x:v>51253</x:v>
+      </x:c>
+      <x:c r="G84" s="10" t="str">
+        <x:v>경남 창원시 마산합포구 자산북4길 8</x:v>
+      </x:c>
+      <x:c r="H84" s="10" t="str">
+        <x:v>1105호</x:v>
+      </x:c>
+      <x:c r="I84" s="10" t="str"/>
+      <x:c r="J84" s="10" t="str">
+        <x:v>1c5aaf08-55d0-4c0a-9edf-d5bc2253749a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:10:15</x:v>
+      </x:c>
+      <x:c r="B85" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C85" s="10" t="str">
+        <x:v>권순묵</x:v>
+      </x:c>
+      <x:c r="D85" s="10" t="str">
+        <x:v>내마음처럼</x:v>
+      </x:c>
+      <x:c r="E85" s="12" t="str">
+        <x:v>010-7650-0141</x:v>
+      </x:c>
+      <x:c r="F85" s="12" t="str">
+        <x:v>31776</x:v>
+      </x:c>
+      <x:c r="G85" s="10" t="str">
+        <x:v>충남 당진시 천변1길 144</x:v>
+      </x:c>
+      <x:c r="H85" s="10" t="str">
+        <x:v>306호</x:v>
+      </x:c>
+      <x:c r="I85" s="10" t="str"/>
+      <x:c r="J85" s="10" t="str">
+        <x:v>a2a0182f-0c71-497d-9889-77b2b7be8f78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:11:30</x:v>
+      </x:c>
+      <x:c r="B86" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C86" s="10" t="str">
+        <x:v>이종환</x:v>
+      </x:c>
+      <x:c r="D86" s="10" t="str">
+        <x:v>다우라</x:v>
+      </x:c>
+      <x:c r="E86" s="12" t="str">
+        <x:v>010-24067679</x:v>
+      </x:c>
+      <x:c r="F86" s="12" t="str">
+        <x:v>50830</x:v>
+      </x:c>
+      <x:c r="G86" s="10" t="str">
+        <x:v>경남 김해시 해반천로278번길 12-27</x:v>
+      </x:c>
+      <x:c r="H86" s="10" t="str">
+        <x:v>108동803호</x:v>
+      </x:c>
+      <x:c r="I86" s="10" t="str"/>
+      <x:c r="J86" s="10" t="str">
+        <x:v>e1287c26-948e-4740-8cd3-24f807a6ab69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:12:17</x:v>
+      </x:c>
+      <x:c r="B87" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C87" s="10" t="str">
+        <x:v>임제성</x:v>
+      </x:c>
+      <x:c r="D87" s="10" t="str">
+        <x:v>동대문</x:v>
+      </x:c>
+      <x:c r="E87" s="12" t="str">
+        <x:v>010-8888-6167</x:v>
+      </x:c>
+      <x:c r="F87" s="12" t="str">
+        <x:v>11426</x:v>
+      </x:c>
+      <x:c r="G87" s="10" t="str">
+        <x:v>경기 양주시 은현면 은남로 226-55</x:v>
+      </x:c>
+      <x:c r="H87" s="10" t="str">
+        <x:v>단독주택</x:v>
+      </x:c>
+      <x:c r="I87" s="10" t="str"/>
+      <x:c r="J87" s="10" t="str">
+        <x:v>aa920674-44d2-4925-a206-ea3e28cbddfe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:13:06</x:v>
+      </x:c>
+      <x:c r="B88" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C88" s="10" t="str">
+        <x:v>두리안</x:v>
+      </x:c>
+      <x:c r="D88" s="10" t="str">
+        <x:v>두리안</x:v>
+      </x:c>
+      <x:c r="E88" s="12" t="str">
+        <x:v>010-8549-3131</x:v>
+      </x:c>
+      <x:c r="F88" s="12" t="str">
+        <x:v>46230</x:v>
+      </x:c>
+      <x:c r="G88" s="10" t="str">
+        <x:v>부산 금정구 중앙대로1929번길 40-6</x:v>
+      </x:c>
+      <x:c r="H88" s="10" t="str"/>
+      <x:c r="I88" s="10" t="str"/>
+      <x:c r="J88" s="10" t="str">
+        <x:v>c25058a2-06b3-4fe8-88ad-644bbf256eba</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:14:22</x:v>
+      </x:c>
+      <x:c r="B89" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C89" s="10" t="str">
+        <x:v>한경희</x:v>
+      </x:c>
+      <x:c r="D89" s="10" t="str">
+        <x:v>들국화</x:v>
+      </x:c>
+      <x:c r="E89" s="12" t="str">
+        <x:v>01032936481</x:v>
+      </x:c>
+      <x:c r="F89" s="12" t="str">
+        <x:v>23011</x:v>
+      </x:c>
+      <x:c r="G89" s="10" t="str">
+        <x:v>인천 강화군 양사면 전망대로1071번길 18</x:v>
+      </x:c>
+      <x:c r="H89" s="10" t="str"/>
+      <x:c r="I89" s="10" t="str"/>
+      <x:c r="J89" s="10" t="str">
+        <x:v>eecbcf0e-0612-4ef0-96e4-c75fec87588e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:15:09</x:v>
+      </x:c>
+      <x:c r="B90" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C90" s="10" t="str">
+        <x:v>박인석</x:v>
+      </x:c>
+      <x:c r="D90" s="10" t="str">
+        <x:v>땅부자농부</x:v>
+      </x:c>
+      <x:c r="E90" s="12" t="str">
+        <x:v>010-5488-7945</x:v>
+      </x:c>
+      <x:c r="F90" s="12" t="str">
+        <x:v>57735</x:v>
+      </x:c>
+      <x:c r="G90" s="10" t="str">
+        <x:v>전남광주통합특별시 광양시 광양읍 호북길 25</x:v>
+      </x:c>
+      <x:c r="H90" s="10" t="str">
+        <x:v>106동402호</x:v>
+      </x:c>
+      <x:c r="I90" s="10" t="str"/>
+      <x:c r="J90" s="10" t="str">
+        <x:v>9cc77be9-017c-4610-82d9-65bcaaee3ba3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:15:41</x:v>
+      </x:c>
+      <x:c r="B91" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C91" s="10" t="str">
+        <x:v>노철종</x:v>
+      </x:c>
+      <x:c r="D91" s="10" t="str">
+        <x:v>또연</x:v>
+      </x:c>
+      <x:c r="E91" s="12" t="str">
+        <x:v>010 4132 3265</x:v>
+      </x:c>
+      <x:c r="F91" s="12" t="str">
+        <x:v>10064</x:v>
+      </x:c>
+      <x:c r="G91" s="10" t="str">
+        <x:v>경기 김포시 운곡로 2</x:v>
+      </x:c>
+      <x:c r="H91" s="10" t="str"/>
+      <x:c r="I91" s="10" t="str"/>
+      <x:c r="J91" s="10" t="str">
+        <x:v>193eabcb-5f91-4b2b-a9ff-a5874cec8acb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:16:31</x:v>
+      </x:c>
+      <x:c r="B92" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C92" s="10" t="str">
+        <x:v>러블리77</x:v>
+      </x:c>
+      <x:c r="D92" s="10" t="str">
+        <x:v>러블리77</x:v>
+      </x:c>
+      <x:c r="E92" s="12" t="str">
+        <x:v>010-2339-3435</x:v>
+      </x:c>
+      <x:c r="F92" s="12" t="str">
+        <x:v>15401</x:v>
+      </x:c>
+      <x:c r="G92" s="10" t="str">
+        <x:v>경기 안산시 단원구 도일로 60-34</x:v>
+      </x:c>
+      <x:c r="H92" s="10" t="str">
+        <x:v>405동102호</x:v>
+      </x:c>
+      <x:c r="I92" s="10" t="str"/>
+      <x:c r="J92" s="10" t="str">
+        <x:v>b8e7a9f8-0800-484e-b7b4-84ae191bc53e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:17:13</x:v>
+      </x:c>
+      <x:c r="B93" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C93" s="10" t="str">
+        <x:v>목원용</x:v>
+      </x:c>
+      <x:c r="D93" s="10" t="str">
+        <x:v>로드</x:v>
+      </x:c>
+      <x:c r="E93" s="12" t="str">
+        <x:v>010-34636317</x:v>
+      </x:c>
+      <x:c r="F93" s="12" t="str">
+        <x:v>35003</x:v>
+      </x:c>
+      <x:c r="G93" s="10" t="str">
+        <x:v>대전 중구 산성로 108-23</x:v>
+      </x:c>
+      <x:c r="H93" s="10" t="str"/>
+      <x:c r="I93" s="10" t="str"/>
+      <x:c r="J93" s="10" t="str">
+        <x:v>825b3bcf-7eda-4973-b0f8-ce48873639bf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:18:07</x:v>
+      </x:c>
+      <x:c r="B94" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C94" s="10" t="str">
+        <x:v>마밥</x:v>
+      </x:c>
+      <x:c r="D94" s="10" t="str">
+        <x:v>마밥7777</x:v>
+      </x:c>
+      <x:c r="E94" s="12" t="str">
+        <x:v>010-2585-0531</x:v>
+      </x:c>
+      <x:c r="F94" s="12" t="str">
+        <x:v>13335</x:v>
+      </x:c>
+      <x:c r="G94" s="10" t="str">
+        <x:v>경기 성남시 수정구 산성대로173번길 3</x:v>
+      </x:c>
+      <x:c r="H94" s="10" t="str">
+        <x:v>201호</x:v>
+      </x:c>
+      <x:c r="I94" s="10" t="str"/>
+      <x:c r="J94" s="10" t="str">
+        <x:v>03cbcf1d-f52f-42c1-9c99-7c7fa5e659ad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:18:53</x:v>
+      </x:c>
+      <x:c r="B95" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C95" s="10" t="str">
+        <x:v>김상길</x:v>
+      </x:c>
+      <x:c r="D95" s="10" t="str">
+        <x:v>머슴</x:v>
+      </x:c>
+      <x:c r="E95" s="12" t="str">
+        <x:v>010 7586 1600</x:v>
+      </x:c>
+      <x:c r="F95" s="12" t="str">
+        <x:v>38628</x:v>
+      </x:c>
+      <x:c r="G95" s="10" t="str">
+        <x:v>경북 경산시 중앙로14길 8-12</x:v>
+      </x:c>
+      <x:c r="H95" s="10" t="str">
+        <x:v>301호</x:v>
+      </x:c>
+      <x:c r="I95" s="10" t="str"/>
+      <x:c r="J95" s="10" t="str">
+        <x:v>ca32ca4f-675d-4570-88db-5447b683a9f3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:19:49</x:v>
+      </x:c>
+      <x:c r="B96" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C96" s="10" t="str">
+        <x:v>김영애</x:v>
+      </x:c>
+      <x:c r="D96" s="10" t="str">
+        <x:v>뭉치짱m7c</x:v>
+      </x:c>
+      <x:c r="E96" s="12" t="str">
+        <x:v>010-8736-9661</x:v>
+      </x:c>
+      <x:c r="F96" s="12" t="str">
+        <x:v>17825</x:v>
+      </x:c>
+      <x:c r="G96" s="10" t="str">
+        <x:v>경기 평택시 은실5길 58-3</x:v>
+      </x:c>
+      <x:c r="H96" s="10" t="str">
+        <x:v>28동401호</x:v>
+      </x:c>
+      <x:c r="I96" s="10" t="str"/>
+      <x:c r="J96" s="10" t="str">
+        <x:v>16efe54c-e5ce-4ab0-b057-149f9fb1189a</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:21:03</x:v>
+      </x:c>
+      <x:c r="B97" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C97" s="10" t="str">
+        <x:v>박현준</x:v>
+      </x:c>
+      <x:c r="D97" s="10" t="str">
+        <x:v>박현준</x:v>
+      </x:c>
+      <x:c r="E97" s="12" t="str">
+        <x:v>010-4415932</x:v>
+      </x:c>
+      <x:c r="F97" s="12" t="str">
+        <x:v>32980</x:v>
+      </x:c>
+      <x:c r="G97" s="10" t="str">
+        <x:v>충남 논산시 시민로 290</x:v>
+      </x:c>
+      <x:c r="H97" s="10" t="str"/>
+      <x:c r="I97" s="10" t="str"/>
+      <x:c r="J97" s="10" t="str">
+        <x:v>06ee6ce3-9c6b-4afc-9e2a-14a1d6c06c11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:24:25</x:v>
+      </x:c>
+      <x:c r="B98" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C98" s="10" t="str">
+        <x:v>권혁삼</x:v>
+      </x:c>
+      <x:c r="D98" s="10" t="str">
+        <x:v>방탄</x:v>
+      </x:c>
+      <x:c r="E98" s="12" t="str">
+        <x:v>010-3528-7447</x:v>
+      </x:c>
+      <x:c r="F98" s="12" t="str">
+        <x:v>36857</x:v>
+      </x:c>
+      <x:c r="G98" s="10" t="str">
+        <x:v>경북 예천군 용궁면 용궁향교길 20</x:v>
+      </x:c>
+      <x:c r="H98" s="10" t="str"/>
+      <x:c r="I98" s="10" t="str"/>
+      <x:c r="J98" s="10" t="str">
+        <x:v>1a324193-b844-4108-a28e-14e8223d7eb6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:25:17</x:v>
+      </x:c>
+      <x:c r="B99" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C99" s="10" t="str">
+        <x:v>유재호</x:v>
+      </x:c>
+      <x:c r="D99" s="10" t="str">
+        <x:v>버들</x:v>
+      </x:c>
+      <x:c r="E99" s="12" t="str">
+        <x:v>010-8713-8999</x:v>
+      </x:c>
+      <x:c r="F99" s="12" t="str">
+        <x:v>21903</x:v>
+      </x:c>
+      <x:c r="G99" s="10" t="str">
+        <x:v>인천 연수구 청학로27번길 11</x:v>
+      </x:c>
+      <x:c r="H99" s="10" t="str">
+        <x:v>2동201호</x:v>
+      </x:c>
+      <x:c r="I99" s="10" t="str"/>
+      <x:c r="J99" s="10" t="str">
+        <x:v>02c4fd6d-ce42-4bbc-9fbb-13e586c2e0c6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:26:02</x:v>
+      </x:c>
+      <x:c r="B100" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C100" s="10" t="str">
+        <x:v>이승복</x:v>
+      </x:c>
+      <x:c r="D100" s="10" t="str">
+        <x:v>별난1004</x:v>
+      </x:c>
+      <x:c r="E100" s="12" t="str">
+        <x:v>01080334844</x:v>
+      </x:c>
+      <x:c r="F100" s="12" t="str">
+        <x:v>17123</x:v>
+      </x:c>
+      <x:c r="G100" s="10" t="str">
+        <x:v>경기 용인시 처인구 이동읍 어진로 723</x:v>
+      </x:c>
+      <x:c r="H100" s="10" t="str">
+        <x:v>별난마켓</x:v>
+      </x:c>
+      <x:c r="I100" s="10" t="str"/>
+      <x:c r="J100" s="10" t="str">
+        <x:v>1279ab56-6576-40cd-aa40-4d71b441c122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:27:23</x:v>
+      </x:c>
+      <x:c r="B101" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C101" s="10" t="str">
+        <x:v>이경락</x:v>
+      </x:c>
+      <x:c r="D101" s="10" t="str">
+        <x:v>부엉이</x:v>
+      </x:c>
+      <x:c r="E101" s="12" t="str">
+        <x:v>010-9363-6966</x:v>
+      </x:c>
+      <x:c r="F101" s="12" t="str">
+        <x:v>38843</x:v>
+      </x:c>
+      <x:c r="G101" s="10" t="str">
+        <x:v>경북 영천시 최무선로 231-1</x:v>
+      </x:c>
+      <x:c r="H101" s="10" t="str">
+        <x:v>1104호</x:v>
+      </x:c>
+      <x:c r="I101" s="10" t="str"/>
+      <x:c r="J101" s="10" t="str">
+        <x:v>927f2ff2-7ba1-4116-9f96-ceb88f6f22f0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:28:18</x:v>
+      </x:c>
+      <x:c r="B102" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C102" s="10" t="str">
+        <x:v>조양선</x:v>
+      </x:c>
+      <x:c r="D102" s="10" t="str">
+        <x:v>블루버드</x:v>
+      </x:c>
+      <x:c r="E102" s="12" t="str">
+        <x:v>010-3861-2231</x:v>
+      </x:c>
+      <x:c r="F102" s="12" t="str">
+        <x:v>44965</x:v>
+      </x:c>
+      <x:c r="G102" s="10" t="str">
+        <x:v>울산 울주군 웅촌면 덕현3길 18</x:v>
+      </x:c>
+      <x:c r="H102" s="10" t="str"/>
+      <x:c r="I102" s="10" t="str"/>
+      <x:c r="J102" s="10" t="str">
+        <x:v>fa7b35a0-1fa2-449c-a256-775ce838aadd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:29:04</x:v>
+      </x:c>
+      <x:c r="B103" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C103" s="10" t="str">
+        <x:v>빠꾸미</x:v>
+      </x:c>
+      <x:c r="D103" s="10" t="str">
+        <x:v>빠꾸미</x:v>
+      </x:c>
+      <x:c r="E103" s="12" t="str">
+        <x:v>010-3135-0754</x:v>
+      </x:c>
+      <x:c r="F103" s="12" t="str">
+        <x:v>53278</x:v>
+      </x:c>
+      <x:c r="G103" s="10" t="str">
+        <x:v>경남 거제시 사등면 두동로 54-40</x:v>
+      </x:c>
+      <x:c r="H103" s="10" t="str">
+        <x:v>204동602호</x:v>
+      </x:c>
+      <x:c r="I103" s="10" t="str"/>
+      <x:c r="J103" s="10" t="str">
+        <x:v>a84562df-9954-4564-a36c-0b184698f192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:29:41</x:v>
+      </x:c>
+      <x:c r="B104" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C104" s="10" t="str">
+        <x:v>김말도</x:v>
+      </x:c>
+      <x:c r="D104" s="10" t="str">
+        <x:v>살찐여우</x:v>
+      </x:c>
+      <x:c r="E104" s="12" t="str">
+        <x:v>010026743614</x:v>
+      </x:c>
+      <x:c r="F104" s="12" t="str">
+        <x:v>40116</x:v>
+      </x:c>
+      <x:c r="G104" s="10" t="str">
+        <x:v>경북 고령군 성산면 성암로 51</x:v>
+      </x:c>
+      <x:c r="H104" s="10" t="str"/>
+      <x:c r="I104" s="10" t="str"/>
+      <x:c r="J104" s="10" t="str">
+        <x:v>7de68edd-ec43-4545-80fa-2c8bdcdbda89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:30:45</x:v>
+      </x:c>
+      <x:c r="B105" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C105" s="10" t="str">
+        <x:v>송공경</x:v>
+      </x:c>
+      <x:c r="D105" s="10" t="str">
+        <x:v>송공경</x:v>
+      </x:c>
+      <x:c r="E105" s="12" t="str">
+        <x:v>01075352810</x:v>
+      </x:c>
+      <x:c r="F105" s="12" t="str">
+        <x:v>41183</x:v>
+      </x:c>
+      <x:c r="G105" s="10" t="str">
+        <x:v>대구 동구 동북로75길 12-3</x:v>
+      </x:c>
+      <x:c r="H105" s="10" t="str"/>
+      <x:c r="I105" s="10" t="str"/>
+      <x:c r="J105" s="10" t="str">
+        <x:v>ebed3905-b06e-4739-bc5e-d3819074536b</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:31:17</x:v>
+      </x:c>
+      <x:c r="B106" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C106" s="10" t="str">
+        <x:v>송채원</x:v>
+      </x:c>
+      <x:c r="D106" s="10" t="str">
+        <x:v>송채원채원</x:v>
+      </x:c>
+      <x:c r="E106" s="12" t="str">
+        <x:v>010-5361-1145</x:v>
+      </x:c>
+      <x:c r="F106" s="12" t="str">
+        <x:v>24264</x:v>
+      </x:c>
+      <x:c r="G106" s="10" t="str">
+        <x:v>강원특별자치도 춘천시 향교뒷길 1</x:v>
+      </x:c>
+      <x:c r="H106" s="10" t="str"/>
+      <x:c r="I106" s="10" t="str"/>
+      <x:c r="J106" s="10" t="str">
+        <x:v>02fbc7f0-77b7-4f8a-ab31-026ce5da1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:33:11</x:v>
+      </x:c>
+      <x:c r="B107" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C107" s="10" t="str">
+        <x:v>김현철</x:v>
+      </x:c>
+      <x:c r="D107" s="10" t="str">
+        <x:v>신성</x:v>
+      </x:c>
+      <x:c r="E107" s="12" t="str">
+        <x:v>010-7752-8565</x:v>
+      </x:c>
+      <x:c r="F107" s="12" t="str">
+        <x:v>42615</x:v>
+      </x:c>
+      <x:c r="G107" s="10" t="str">
+        <x:v>대구 달서구 선원남로 99</x:v>
+      </x:c>
+      <x:c r="H107" s="10" t="str">
+        <x:v>312동1904호</x:v>
+      </x:c>
+      <x:c r="I107" s="10" t="str"/>
+      <x:c r="J107" s="10" t="str">
+        <x:v>9724c338-2de0-471a-baaf-72d2e5cd7813</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:34:05</x:v>
+      </x:c>
+      <x:c r="B108" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C108" s="10" t="str">
+        <x:v>아델라</x:v>
+      </x:c>
+      <x:c r="D108" s="10" t="str">
+        <x:v>아델라</x:v>
+      </x:c>
+      <x:c r="E108" s="12" t="str">
+        <x:v>010-93043994</x:v>
+      </x:c>
+      <x:c r="F108" s="12" t="str">
+        <x:v>50451</x:v>
+      </x:c>
+      <x:c r="G108" s="10" t="str">
+        <x:v>경남 밀양시 상남면 운하길 20</x:v>
+      </x:c>
+      <x:c r="H108" s="10" t="str"/>
+      <x:c r="I108" s="10" t="str"/>
+      <x:c r="J108" s="10" t="str">
+        <x:v>feb53e24-c669-40e3-b2ee-e75065b0e236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:35:09</x:v>
+      </x:c>
+      <x:c r="B109" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C109" s="10" t="str">
+        <x:v>양서</x:v>
+      </x:c>
+      <x:c r="D109" s="10" t="str">
+        <x:v>양서</x:v>
+      </x:c>
+      <x:c r="E109" s="12" t="str">
+        <x:v>01089711008</x:v>
+      </x:c>
+      <x:c r="F109" s="12" t="str">
+        <x:v>07348</x:v>
+      </x:c>
+      <x:c r="G109" s="10" t="str">
+        <x:v>서울 영등포구 도신로54길 5-3</x:v>
+      </x:c>
+      <x:c r="H109" s="10" t="str"/>
+      <x:c r="I109" s="10" t="str"/>
+      <x:c r="J109" s="10" t="str">
+        <x:v>8afd818f-ee1d-4376-89d4-d3ada1dbd126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:35:52</x:v>
+      </x:c>
+      <x:c r="B110" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C110" s="10" t="str">
+        <x:v>양섬윤</x:v>
+      </x:c>
+      <x:c r="D110" s="10" t="str">
+        <x:v>양섬윤</x:v>
+      </x:c>
+      <x:c r="E110" s="12" t="str">
+        <x:v>010-8445-3531</x:v>
+      </x:c>
+      <x:c r="F110" s="12" t="str">
+        <x:v>21641</x:v>
+      </x:c>
+      <x:c r="G110" s="10" t="str">
+        <x:v>인천 남동구 은봉로166번길 27</x:v>
+      </x:c>
+      <x:c r="H110" s="10" t="str">
+        <x:v>210동1003호</x:v>
+      </x:c>
+      <x:c r="I110" s="10" t="str"/>
+      <x:c r="J110" s="10" t="str">
+        <x:v>564e3b2a-26de-48ba-bf0e-a11eb7667497</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:36:34</x:v>
+      </x:c>
+      <x:c r="B111" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C111" s="10" t="str">
+        <x:v>장현길</x:v>
+      </x:c>
+      <x:c r="D111" s="10" t="str">
+        <x:v>어화둥둥</x:v>
+      </x:c>
+      <x:c r="E111" s="12" t="str">
+        <x:v>01052567155</x:v>
+      </x:c>
+      <x:c r="F111" s="12" t="str">
+        <x:v>49088</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>부산 영도구 태종로 422</x:v>
+      </x:c>
+      <x:c r="H111" s="10" t="str">
+        <x:v>302호</x:v>
+      </x:c>
+      <x:c r="I111" s="10" t="str"/>
+      <x:c r="J111" s="10" t="str">
+        <x:v>8dc31d37-e7e9-4140-af18-7a2cfb32f939</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:37:43</x:v>
+      </x:c>
+      <x:c r="B112" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C112" s="10" t="str">
+        <x:v>이도형</x:v>
+      </x:c>
+      <x:c r="D112" s="10" t="str">
+        <x:v>영구네</x:v>
+      </x:c>
+      <x:c r="E112" s="12" t="str">
+        <x:v>010-3684-4331</x:v>
+      </x:c>
+      <x:c r="F112" s="12" t="str">
+        <x:v>32416</x:v>
+      </x:c>
+      <x:c r="G112" s="10" t="str">
+        <x:v>충남 예산군 삽교읍 다락로 157-22</x:v>
+      </x:c>
+      <x:c r="H112" s="10" t="str"/>
+      <x:c r="I112" s="10" t="str"/>
+      <x:c r="J112" s="10" t="str">
+        <x:v>d30e8b35-269c-4f2f-af94-7daa44927d56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:38:53</x:v>
+      </x:c>
+      <x:c r="B113" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C113" s="10" t="str">
+        <x:v>이재윤</x:v>
+      </x:c>
+      <x:c r="D113" s="10" t="str">
+        <x:v>오니숍터</x:v>
+      </x:c>
+      <x:c r="E113" s="12" t="str">
+        <x:v>01086034857</x:v>
+      </x:c>
+      <x:c r="F113" s="12" t="str">
+        <x:v>41511</x:v>
+      </x:c>
+      <x:c r="G113" s="10" t="str">
+        <x:v>대구 북구 검단로41길 11</x:v>
+      </x:c>
+      <x:c r="H113" s="10" t="str">
+        <x:v>검단동 1동</x:v>
+      </x:c>
+      <x:c r="I113" s="10" t="str"/>
+      <x:c r="J113" s="10" t="str">
+        <x:v>d9ce9878-fde4-4b7a-a4b4-9926db72d7be</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:39:59</x:v>
+      </x:c>
+      <x:c r="B114" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C114" s="10" t="str">
+        <x:v>성민서</x:v>
+      </x:c>
+      <x:c r="D114" s="10" t="str">
+        <x:v>용문산</x:v>
+      </x:c>
+      <x:c r="E114" s="12" t="str">
+        <x:v>01092434120</x:v>
+      </x:c>
+      <x:c r="F114" s="12" t="str">
+        <x:v>34067</x:v>
+      </x:c>
+      <x:c r="G114" s="10" t="str">
+        <x:v>대전 유성구 반석서로 109</x:v>
+      </x:c>
+      <x:c r="H114" s="10" t="str">
+        <x:v>701동2502호</x:v>
+      </x:c>
+      <x:c r="I114" s="10" t="str"/>
+      <x:c r="J114" s="10" t="str">
+        <x:v>8a3b48f2-0496-43b9-bf72-54550dc0c9e4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:40:46</x:v>
+      </x:c>
+      <x:c r="B115" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C115" s="10" t="str">
+        <x:v>진창용</x:v>
+      </x:c>
+      <x:c r="D115" s="10" t="str">
+        <x:v>용용</x:v>
+      </x:c>
+      <x:c r="E115" s="12" t="str">
+        <x:v>01048182318</x:v>
+      </x:c>
+      <x:c r="F115" s="12" t="str">
+        <x:v>17859</x:v>
+      </x:c>
+      <x:c r="G115" s="10" t="str">
+        <x:v>경기 평택시 비전2로 320</x:v>
+      </x:c>
+      <x:c r="H115" s="10" t="str">
+        <x:v>505동1207호</x:v>
+      </x:c>
+      <x:c r="I115" s="10" t="str"/>
+      <x:c r="J115" s="10" t="str">
+        <x:v>87ef3c72-3247-49f8-a270-3b0c3cf8c1e6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:41:31</x:v>
+      </x:c>
+      <x:c r="B116" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C116" s="10" t="str">
+        <x:v>우종환</x:v>
+      </x:c>
+      <x:c r="D116" s="10" t="str">
+        <x:v>우종환</x:v>
+      </x:c>
+      <x:c r="E116" s="12" t="str">
+        <x:v>01095007258</x:v>
+      </x:c>
+      <x:c r="F116" s="12" t="str">
+        <x:v>34652</x:v>
+      </x:c>
+      <x:c r="G116" s="10" t="str">
+        <x:v>대전 동구 대학로 8-3</x:v>
+      </x:c>
+      <x:c r="H116" s="10" t="str">
+        <x:v>304호</x:v>
+      </x:c>
+      <x:c r="I116" s="10" t="str"/>
+      <x:c r="J116" s="10" t="str">
+        <x:v>f1ffa923-d3ac-4c19-8356-21b0a4e24cdc</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:42:58</x:v>
+      </x:c>
+      <x:c r="B117" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C117" s="10" t="str">
+        <x:v>유강수</x:v>
+      </x:c>
+      <x:c r="D117" s="10" t="str">
+        <x:v>유강수</x:v>
+      </x:c>
+      <x:c r="E117" s="12" t="str">
+        <x:v>01035683377</x:v>
+      </x:c>
+      <x:c r="F117" s="12" t="str">
+        <x:v>50322</x:v>
+      </x:c>
+      <x:c r="G117" s="10" t="str">
+        <x:v>경남 창녕군 창녕읍 창녕대로 276</x:v>
+      </x:c>
+      <x:c r="H117" s="10" t="str"/>
+      <x:c r="I117" s="10" t="str"/>
+      <x:c r="J117" s="10" t="str">
+        <x:v>be8d94c8-40fa-4940-98c2-5b64bbca544e</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:43:49</x:v>
+      </x:c>
+      <x:c r="B118" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C118" s="10" t="str">
+        <x:v>이정표</x:v>
+      </x:c>
+      <x:c r="D118" s="10" t="str">
+        <x:v>이정표</x:v>
+      </x:c>
+      <x:c r="E118" s="12" t="str">
+        <x:v>010-3786-9001</x:v>
+      </x:c>
+      <x:c r="F118" s="12" t="str">
+        <x:v>05116</x:v>
+      </x:c>
+      <x:c r="G118" s="10" t="str">
+        <x:v>서울 광진구 광나루로56길 85</x:v>
+      </x:c>
+      <x:c r="H118" s="10" t="str">
+        <x:v>2층c40호</x:v>
+      </x:c>
+      <x:c r="I118" s="10" t="str"/>
+      <x:c r="J118" s="10" t="str">
+        <x:v>cc2ffa7e-9006-486a-8182-ab41fea8fb6b</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:44:39</x:v>
+      </x:c>
+      <x:c r="B119" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C119" s="10" t="str">
+        <x:v>이창휘</x:v>
+      </x:c>
+      <x:c r="D119" s="10" t="str">
+        <x:v>이창휘</x:v>
+      </x:c>
+      <x:c r="E119" s="12" t="str">
+        <x:v>01064870074</x:v>
+      </x:c>
+      <x:c r="F119" s="12" t="str">
+        <x:v>16986</x:v>
+      </x:c>
+      <x:c r="G119" s="10" t="str">
+        <x:v>경기 용인시 기흥구 어정로 87-6</x:v>
+      </x:c>
+      <x:c r="H119" s="10" t="str">
+        <x:v>소키타운B동405호</x:v>
+      </x:c>
+      <x:c r="I119" s="10" t="str"/>
+      <x:c r="J119" s="10" t="str">
+        <x:v>c41a7e13-b04a-4230-bf50-ddf02682a83f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:45:19</x:v>
+      </x:c>
+      <x:c r="B120" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C120" s="10" t="str">
+        <x:v>이햔숙</x:v>
+      </x:c>
+      <x:c r="D120" s="10" t="str">
+        <x:v>이현숙</x:v>
+      </x:c>
+      <x:c r="E120" s="12" t="str">
+        <x:v>01026910677</x:v>
+      </x:c>
+      <x:c r="F120" s="12" t="str">
+        <x:v>53076</x:v>
+      </x:c>
+      <x:c r="G120" s="10" t="str">
+        <x:v>경남 통영시 도남로 150-6</x:v>
+      </x:c>
+      <x:c r="H120" s="10" t="str"/>
+      <x:c r="I120" s="10" t="str"/>
+      <x:c r="J120" s="10" t="str">
+        <x:v>791abf55-b430-4e4c-bd46-b1ee0978a581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:46:30</x:v>
+      </x:c>
+      <x:c r="B121" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C121" s="10" t="str">
+        <x:v>정미신</x:v>
+      </x:c>
+      <x:c r="D121" s="10" t="str">
+        <x:v>정미신</x:v>
+      </x:c>
+      <x:c r="E121" s="12" t="str">
+        <x:v>01073859275</x:v>
+      </x:c>
+      <x:c r="F121" s="12" t="str">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="G121" s="10" t="str">
+        <x:v>부산 금정구 중앙대로2007번길 22-1</x:v>
+      </x:c>
+      <x:c r="H121" s="10" t="str">
+        <x:v>101호</x:v>
+      </x:c>
+      <x:c r="I121" s="10" t="str"/>
+      <x:c r="J121" s="10" t="str">
+        <x:v>55ddf7ac-5bd8-4324-a985-0f10e9619541</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:47:55</x:v>
+      </x:c>
+      <x:c r="B122" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C122" s="10" t="str">
+        <x:v>정철배</x:v>
+      </x:c>
+      <x:c r="D122" s="10" t="str">
+        <x:v>정철배</x:v>
+      </x:c>
+      <x:c r="E122" s="12" t="str">
+        <x:v>010-5875-6820</x:v>
+      </x:c>
+      <x:c r="F122" s="12" t="str">
+        <x:v>50815</x:v>
+      </x:c>
+      <x:c r="G122" s="10" t="str">
+        <x:v>경남 김해시 삼안로 226</x:v>
+      </x:c>
+      <x:c r="H122" s="10" t="str">
+        <x:v>106동802호</x:v>
+      </x:c>
+      <x:c r="I122" s="10" t="str"/>
+      <x:c r="J122" s="10" t="str">
+        <x:v>4c179a0f-8279-4b1e-ac78-5ae4102f7ef9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:49:15</x:v>
+      </x:c>
+      <x:c r="B123" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C123" s="10" t="str">
+        <x:v>조나단</x:v>
+      </x:c>
+      <x:c r="D123" s="10" t="str">
+        <x:v>조나단</x:v>
+      </x:c>
+      <x:c r="E123" s="12" t="str">
+        <x:v>01077578182</x:v>
+      </x:c>
+      <x:c r="F123" s="12" t="str">
+        <x:v>61501</x:v>
+      </x:c>
+      <x:c r="G123" s="10" t="str">
+        <x:v>전남광주통합특별시 동구 학소로76번길 14</x:v>
+      </x:c>
+      <x:c r="H123" s="10" t="str">
+        <x:v>모아미래도@103동1501호</x:v>
+      </x:c>
+      <x:c r="I123" s="10" t="str"/>
+      <x:c r="J123" s="10" t="str">
+        <x:v>b865b724-86ef-4f25-9813-570a53c4fe9b</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:50:04</x:v>
+      </x:c>
+      <x:c r="B124" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C124" s="10" t="str">
+        <x:v>양현석</x:v>
+      </x:c>
+      <x:c r="D124" s="10" t="str">
+        <x:v>짠지</x:v>
+      </x:c>
+      <x:c r="E124" s="12" t="str">
+        <x:v>01094750741</x:v>
+      </x:c>
+      <x:c r="F124" s="12" t="str">
+        <x:v>27845</x:v>
+      </x:c>
+      <x:c r="G124" s="10" t="str">
+        <x:v>충북 진천군 진천읍 송두3길 7</x:v>
+      </x:c>
+      <x:c r="H124" s="10" t="str"/>
+      <x:c r="I124" s="10" t="str"/>
+      <x:c r="J124" s="10" t="str">
+        <x:v>c55e8f12-1f1a-41e2-895b-eeb4b22647ec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:50:54</x:v>
+      </x:c>
+      <x:c r="B125" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C125" s="10" t="str">
+        <x:v>김찬호</x:v>
+      </x:c>
+      <x:c r="D125" s="10" t="str">
+        <x:v>찬호김</x:v>
+      </x:c>
+      <x:c r="E125" s="12" t="str">
+        <x:v>01046289434</x:v>
+      </x:c>
+      <x:c r="F125" s="12" t="str">
+        <x:v>33327</x:v>
+      </x:c>
+      <x:c r="G125" s="10" t="str">
+        <x:v>충남 청양군 청양읍 중앙로12길 3</x:v>
+      </x:c>
+      <x:c r="H125" s="10" t="str"/>
+      <x:c r="I125" s="10" t="str"/>
+      <x:c r="J125" s="10" t="str">
+        <x:v>1ecabafc-c0ff-4234-8b3b-7092ccb07c76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:51:39</x:v>
+      </x:c>
+      <x:c r="B126" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C126" s="10" t="str">
+        <x:v>최성필</x:v>
+      </x:c>
+      <x:c r="D126" s="10" t="str">
+        <x:v>최성필</x:v>
+      </x:c>
+      <x:c r="E126" s="12" t="str">
+        <x:v>01087222694</x:v>
+      </x:c>
+      <x:c r="F126" s="12" t="str">
+        <x:v>22319</x:v>
+      </x:c>
+      <x:c r="G126" s="10" t="str">
+        <x:v>인천 제물포구 율목로32번길 10</x:v>
+      </x:c>
+      <x:c r="H126" s="10" t="str"/>
+      <x:c r="I126" s="10" t="str"/>
+      <x:c r="J126" s="10" t="str">
+        <x:v>192fd413-e6c6-4be0-8b39-0a0a3cf03a28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:53:02</x:v>
+      </x:c>
+      <x:c r="B127" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C127" s="10" t="str">
+        <x:v>이지미</x:v>
+      </x:c>
+      <x:c r="D127" s="10" t="str">
+        <x:v>택배팀찌미</x:v>
+      </x:c>
+      <x:c r="E127" s="12" t="str">
+        <x:v>01090832936</x:v>
+      </x:c>
+      <x:c r="F127" s="12" t="str">
+        <x:v>10016</x:v>
+      </x:c>
+      <x:c r="G127" s="10" t="str">
+        <x:v>경기 김포시 통진읍 담터로 25-1</x:v>
+      </x:c>
+      <x:c r="H127" s="10" t="str">
+        <x:v>제리안204동 402호</x:v>
+      </x:c>
+      <x:c r="I127" s="10" t="str"/>
+      <x:c r="J127" s="10" t="str">
+        <x:v>5c9952c1-5601-466a-ad03-d12dd3b736eb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:53:55</x:v>
+      </x:c>
+      <x:c r="B128" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C128" s="10" t="str">
+        <x:v>강승준</x:v>
+      </x:c>
+      <x:c r="D128" s="10" t="str">
+        <x:v>토비토토</x:v>
+      </x:c>
+      <x:c r="E128" s="12" t="str">
+        <x:v>01089820865</x:v>
+      </x:c>
+      <x:c r="F128" s="12" t="str">
+        <x:v>13618</x:v>
+      </x:c>
+      <x:c r="G128" s="10" t="str">
+        <x:v>경기 성남시 분당구 미금로 215</x:v>
+      </x:c>
+      <x:c r="H128" s="10" t="str">
+        <x:v>청솔마을 807동1204호 13618</x:v>
+      </x:c>
+      <x:c r="I128" s="10" t="str"/>
+      <x:c r="J128" s="10" t="str">
+        <x:v>edd7850b-52c4-47ad-aef4-db56bdc209b8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:54:33</x:v>
+      </x:c>
+      <x:c r="B129" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C129" s="10" t="str">
+        <x:v>안범석</x:v>
+      </x:c>
+      <x:c r="D129" s="10" t="str">
+        <x:v>파도소리</x:v>
+      </x:c>
+      <x:c r="E129" s="12" t="str">
+        <x:v>01027104473</x:v>
+      </x:c>
+      <x:c r="F129" s="12" t="str">
+        <x:v>10948</x:v>
+      </x:c>
+      <x:c r="G129" s="10" t="str">
+        <x:v>경기 파주시 광탄면 혜음로 1112</x:v>
+      </x:c>
+      <x:c r="H129" s="10" t="str">
+        <x:v>빼돌린천지뒷고기</x:v>
+      </x:c>
+      <x:c r="I129" s="10" t="str"/>
+      <x:c r="J129" s="10" t="str">
+        <x:v>c01ccd10-599d-490f-82bd-53b3f0786ad2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:55:07</x:v>
+      </x:c>
+      <x:c r="B130" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C130" s="10" t="str">
+        <x:v>한은영</x:v>
+      </x:c>
+      <x:c r="D130" s="10" t="str">
+        <x:v>파비</x:v>
+      </x:c>
+      <x:c r="E130" s="12" t="str">
+        <x:v>01059202363</x:v>
+      </x:c>
+      <x:c r="F130" s="12" t="str">
+        <x:v>02246</x:v>
+      </x:c>
+      <x:c r="G130" s="10" t="str">
+        <x:v>서울 중랑구 답십리로77길 20</x:v>
+      </x:c>
+      <x:c r="H130" s="10" t="str">
+        <x:v>401호</x:v>
+      </x:c>
+      <x:c r="I130" s="10" t="str"/>
+      <x:c r="J130" s="10" t="str">
+        <x:v>031169f7-0c76-4f71-a5c5-28cb523d9534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="10" t="str">
+        <x:v>2026. 7. 24. 오후 11:55:46</x:v>
+      </x:c>
+      <x:c r="B131" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C131" s="10" t="str">
+        <x:v>평범한일상</x:v>
+      </x:c>
+      <x:c r="D131" s="10" t="str">
+        <x:v>평범한일상</x:v>
+      </x:c>
+      <x:c r="E131" s="12" t="str">
+        <x:v>01094793818</x:v>
+      </x:c>
+      <x:c r="F131" s="12" t="str">
+        <x:v>12044</x:v>
+      </x:c>
+      <x:c r="G131" s="10" t="str">
+        <x:v>경기 남양주시 오남읍 진건오남로759번길 110</x:v>
+      </x:c>
+      <x:c r="H131" s="10" t="str">
+        <x:v>106동401호</x:v>
+      </x:c>
+      <x:c r="I131" s="10" t="str"/>
+      <x:c r="J131" s="10" t="str">
+        <x:v>a275a401-91d3-4fe1-b8a3-fd84db348316</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="10" t="str">
+        <x:v>2026. 7. 25. 오전 12:00:50</x:v>
+      </x:c>
+      <x:c r="B132" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C132" s="10" t="str">
+        <x:v>김용환</x:v>
+      </x:c>
+      <x:c r="D132" s="10" t="str">
+        <x:v>하우</x:v>
+      </x:c>
+      <x:c r="E132" s="12" t="str">
+        <x:v>01065197370</x:v>
+      </x:c>
+      <x:c r="F132" s="12" t="str">
+        <x:v>47804</x:v>
+      </x:c>
+      <x:c r="G132" s="10" t="str">
+        <x:v>부산 동래구 동래로179번길 49</x:v>
+      </x:c>
+      <x:c r="H132" s="10" t="str">
+        <x:v>201호</x:v>
+      </x:c>
+      <x:c r="I132" s="10" t="str"/>
+      <x:c r="J132" s="10" t="str">
+        <x:v>c374323c-715f-4b74-881b-2dd330d84cf9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="10" t="str">
+        <x:v>2026. 7. 25. 오전 12:02:36</x:v>
+      </x:c>
+      <x:c r="B133" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C133" s="10" t="str">
+        <x:v>이현주</x:v>
+      </x:c>
+      <x:c r="D133" s="10" t="str">
+        <x:v>현주이</x:v>
+      </x:c>
+      <x:c r="E133" s="12" t="str">
+        <x:v>01049941803</x:v>
+      </x:c>
+      <x:c r="F133" s="12" t="str">
+        <x:v>55094</x:v>
+      </x:c>
+      <x:c r="G133" s="10" t="str">
+        <x:v>전북특별자치도 전주시 완산구 효동3길 33</x:v>
+      </x:c>
+      <x:c r="H133" s="10" t="str">
+        <x:v>2동802호</x:v>
+      </x:c>
+      <x:c r="I133" s="10" t="str"/>
+      <x:c r="J133" s="10" t="str">
+        <x:v>9f77b935-b0b5-4e37-baea-d1cb78a8e11f</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="10" t="str">
+        <x:v>2026. 7. 25. 오전 12:04:20</x:v>
+      </x:c>
+      <x:c r="B134" s="10" t="str">
+        <x:v>관리자폼</x:v>
+      </x:c>
+      <x:c r="C134" s="10" t="str">
+        <x:v>이은화</x:v>
+      </x:c>
+      <x:c r="D134" s="10" t="str">
+        <x:v>화니</x:v>
+      </x:c>
+      <x:c r="E134" s="12" t="str">
+        <x:v>01095152949</x:v>
+      </x:c>
+      <x:c r="F134" s="12" t="str">
+        <x:v>47534</x:v>
+      </x:c>
+      <x:c r="G134" s="10" t="str">
+        <x:v>부산 연제구 해맞이로77번길 13</x:v>
+      </x:c>
+      <x:c r="H134" s="10" t="str">
+        <x:v>302호</x:v>
+      </x:c>
+      <x:c r="I134" s="10" t="str"/>
+      <x:c r="J134" s="10" t="str">
+        <x:v>7850521a-164a-4512-8907-81084a14f839</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree26956a202c49cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd136ec8363f44f51"/>
   </x:tableParts>
 </x:worksheet>
 </file>